--- a/Employee_Reports_wi48/Noey Francisco Canonizado Q0621.xlsx
+++ b/Employee_Reports_wi48/Noey Francisco Canonizado Q0621.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>12-Jul-2028</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>469</v>
+        <v>727</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cool Room (Cargo Trainings)</t>
+          <t>Truck dock 20FT (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-011</t>
+          <t>LSME-CRG-M-020</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1099,20 +1099,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>13-Jul-2026</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>12-Jul-2028</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>469</v>
+        <v>727</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Climate Control Center (Cargo Trainings)</t>
+          <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-014</t>
+          <t>LSME-CRG-M-011</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1177,40 +1177,40 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Lodige LOTO Procedure (SOPs)</t>
+          <t>Climate Control Center (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>ELECTRICAL SAFETY</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>LSME-OHS-SOP-021</t>
+          <t>LSME-CRG-M-014</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>20-Oct-2025</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
+          <t>25-Oct-2027</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>99</v>
+        <v>466</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1226,18 +1226,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Equipment Operation Procedure
-(SOP-031) (SOPs)</t>
+          <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-031</t>
+          <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1247,20 +1246,20 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>20-Oct-2025</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1276,7 +1275,8 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+          <t>Equipment Operation Procedure
+(SOP-031) (SOPs)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-028</t>
+          <t>LSME-CRG-SOP-031</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
+          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-035</t>
+          <t>LSME-CRG-SOP-028</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1345,20 +1345,20 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>05-May-2027</t>
+          <t>25-Oct-2026</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>296</v>
+        <v>101</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
+          <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>LSME-IMS-SOP-021</t>
+          <t>LSME-CRG-SOP-035</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
+          <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-030</t>
+          <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1443,20 +1443,20 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>04-May-2027</t>
+          <t>05-May-2027</t>
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1472,17 +1472,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
+          <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>LSME-IMS-SOP-018</t>
+          <t>LSME-CRG-SOP-030</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1492,20 +1492,20 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>05-May-2027</t>
+          <t>04-May-2027</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1521,28 +1521,40 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
+          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-018</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>04-May-2027</t>
+          <t>05-May-2027</t>
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1558,28 +1570,40 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
+          <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>04-May-2027</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1595,7 +1619,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -1612,11 +1636,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1632,48 +1656,85 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>25-Oct-2025</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>25-Oct-2026</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>Matar LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>MATAR</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>FM-DE-24-SOP-SA-013</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>31-Dec-2025</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>31-Dec-2026</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2020,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2083,16 +2144,16 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>18-Mar-2048</t>
+          <t>06-Jun-2048</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7919</v>
+        <v>7996</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2112,16 +2173,16 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>23-Mar-2048</t>
+          <t>06-Jun-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7924</v>
+        <v>7996</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2141,16 +2202,16 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>23-Mar-2048</t>
+          <t>06-Jun-2048</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7924</v>
+        <v>7996</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2158,6 +2219,93 @@
         </is>
       </c>
       <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Chain Elongation -H9TV</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Chain Elongation -Truck Dock</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Chain Cleaning And Lubrication-Truck Dock</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>06-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>7996</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2245,7 +2393,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2274,7 +2422,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2303,7 +2451,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2332,7 +2480,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2361,7 +2509,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2390,7 +2538,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2419,7 +2567,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2448,7 +2596,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2477,7 +2625,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2506,7 +2654,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2535,7 +2683,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2564,7 +2712,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2741,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2622,7 +2770,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2651,7 +2799,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2680,7 +2828,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2709,7 +2857,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2738,7 +2886,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2767,7 +2915,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2796,7 +2944,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2825,7 +2973,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
